--- a/artfynd/A 25811-2025 artfynd.xlsx
+++ b/artfynd/A 25811-2025 artfynd.xlsx
@@ -1700,38 +1700,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126449587</v>
+        <v>126449868</v>
       </c>
       <c r="B11" t="n">
-        <v>95964</v>
+        <v>91265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1739,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571145</v>
+        <v>571218</v>
       </c>
       <c r="R11" t="n">
-        <v>6338773</v>
+        <v>6338786</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1812,41 +1815,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126449868</v>
+        <v>126449587</v>
       </c>
       <c r="B12" t="n">
-        <v>91265</v>
+        <v>95964</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571218</v>
+        <v>571145</v>
       </c>
       <c r="R12" t="n">
-        <v>6338786</v>
+        <v>6338773</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 25811-2025 artfynd.xlsx
+++ b/artfynd/A 25811-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126449977</v>
+        <v>126449558</v>
       </c>
       <c r="B9" t="n">
-        <v>58334</v>
+        <v>95964</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,35 +1480,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1516,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571238</v>
+        <v>571166</v>
       </c>
       <c r="R9" t="n">
-        <v>6338573</v>
+        <v>6338741</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1570,6 +1562,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1588,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126449558</v>
+        <v>126449977</v>
       </c>
       <c r="B10" t="n">
-        <v>95964</v>
+        <v>58334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,27 +1592,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1627,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571166</v>
+        <v>571238</v>
       </c>
       <c r="R10" t="n">
-        <v>6338741</v>
+        <v>6338573</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1682,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25811-2025 artfynd.xlsx
+++ b/artfynd/A 25811-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126449558</v>
+        <v>126449977</v>
       </c>
       <c r="B9" t="n">
-        <v>95964</v>
+        <v>58334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,27 +1480,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571166</v>
+        <v>571238</v>
       </c>
       <c r="R9" t="n">
-        <v>6338741</v>
+        <v>6338573</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1570,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1581,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126449977</v>
+        <v>126449558</v>
       </c>
       <c r="B10" t="n">
-        <v>58334</v>
+        <v>95964</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,35 +1599,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571238</v>
+        <v>571166</v>
       </c>
       <c r="R10" t="n">
-        <v>6338573</v>
+        <v>6338741</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1682,6 +1681,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1700,41 +1700,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126449868</v>
+        <v>126449587</v>
       </c>
       <c r="B11" t="n">
-        <v>91265</v>
+        <v>95964</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1742,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571218</v>
+        <v>571145</v>
       </c>
       <c r="R11" t="n">
-        <v>6338786</v>
+        <v>6338773</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1815,38 +1812,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126449587</v>
+        <v>126449868</v>
       </c>
       <c r="B12" t="n">
-        <v>95964</v>
+        <v>91265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571145</v>
+        <v>571218</v>
       </c>
       <c r="R12" t="n">
-        <v>6338773</v>
+        <v>6338786</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 25811-2025 artfynd.xlsx
+++ b/artfynd/A 25811-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126449977</v>
+        <v>126449558</v>
       </c>
       <c r="B9" t="n">
-        <v>58334</v>
+        <v>95964</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,35 +1480,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1516,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571238</v>
+        <v>571166</v>
       </c>
       <c r="R9" t="n">
-        <v>6338573</v>
+        <v>6338741</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1570,6 +1562,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1588,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126449558</v>
+        <v>126449977</v>
       </c>
       <c r="B10" t="n">
-        <v>95964</v>
+        <v>58334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,27 +1592,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1627,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571166</v>
+        <v>571238</v>
       </c>
       <c r="R10" t="n">
-        <v>6338741</v>
+        <v>6338573</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1682,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1700,41 +1700,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126449868</v>
+        <v>126449587</v>
       </c>
       <c r="B11" t="n">
-        <v>91265</v>
+        <v>95964</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1742,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571218</v>
+        <v>571145</v>
       </c>
       <c r="R11" t="n">
-        <v>6338786</v>
+        <v>6338773</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1815,38 +1812,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126449587</v>
+        <v>126449868</v>
       </c>
       <c r="B12" t="n">
-        <v>95964</v>
+        <v>91265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571145</v>
+        <v>571218</v>
       </c>
       <c r="R12" t="n">
-        <v>6338773</v>
+        <v>6338786</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 25811-2025 artfynd.xlsx
+++ b/artfynd/A 25811-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126449558</v>
+        <v>126449977</v>
       </c>
       <c r="B9" t="n">
-        <v>95964</v>
+        <v>58334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,27 +1480,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571166</v>
+        <v>571238</v>
       </c>
       <c r="R9" t="n">
-        <v>6338741</v>
+        <v>6338573</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1570,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1581,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126449977</v>
+        <v>126449558</v>
       </c>
       <c r="B10" t="n">
-        <v>58334</v>
+        <v>95964</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,35 +1599,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571238</v>
+        <v>571166</v>
       </c>
       <c r="R10" t="n">
-        <v>6338573</v>
+        <v>6338741</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1682,6 +1681,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
